--- a/xls/square_un_16_tri3_14_0.xlsx
+++ b/xls/square_un_16_tri3_14_0.xlsx
@@ -482,13 +482,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-14.765701885378936</v>
+        <v>9.214341633182652</v>
       </c>
       <c r="J16">
-        <v>-14.211944479394369</v>
+        <v>9.120132936993242</v>
       </c>
       <c r="K16">
-        <v>-13.47210588384233</v>
+        <v>8.897724794194058</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_14_0.xlsx
+++ b/xls/square_un_16_tri3_14_0.xlsx
@@ -482,13 +482,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>9.214341633182652</v>
+        <v>-1.9321645089236033</v>
       </c>
       <c r="J16">
-        <v>9.120132936993242</v>
+        <v>-1.637055779240412</v>
       </c>
       <c r="K16">
-        <v>8.897724794194058</v>
+        <v>-0.25487104823900425</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_14_0.xlsx
+++ b/xls/square_un_16_tri3_14_0.xlsx
@@ -461,34 +461,34 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1842</v>
+        <v>1596</v>
       </c>
       <c r="I16">
-        <v>-1.9321645089236033</v>
+        <v>-2.0865303143151412</v>
       </c>
       <c r="J16">
-        <v>-1.637055779240412</v>
+        <v>-1.7746815496210704</v>
       </c>
       <c r="K16">
-        <v>-0.25487104823900425</v>
+        <v>-0.422972193242754</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_14_0.xlsx
+++ b/xls/square_un_16_tri3_14_0.xlsx
@@ -482,13 +482,13 @@
         <v>1596</v>
       </c>
       <c r="I16">
-        <v>-2.0865303143151412</v>
+        <v>-2.086283462949521</v>
       </c>
       <c r="J16">
-        <v>-1.7746815496210704</v>
+        <v>-1.7745261188482686</v>
       </c>
       <c r="K16">
-        <v>-0.422972193242754</v>
+        <v>-0.42329788604874896</v>
       </c>
     </row>
   </sheetData>
